--- a/medical_surveys_questionnaires/050_healthcare_professional_citizenship_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/050_healthcare_professional_citizenship_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Healthcare Professional Citizenship Survey Form Section 1 1 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Healthcare Professional Citizenship Survey Form Section 3 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Quality improvement</t>
+          <t>Healthcare Professional Citizenship Survey Form Section 4 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Healthcare Professional Citizenship Survey Form Section 4 1 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -912,17 +912,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>healthcare_professional_citizenship_survey_form_section_1_choices</t>
+          <t>healthcare_professional_citizenship_survey_form_section_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>less_than_once_a_month</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Less than once a month</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>less_than_once_a_month</t>
+          <t>about_once_a_month</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Less than once a month</t>
+          <t>About once a month</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>about_once_a_month</t>
+          <t>several_times_a_month</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>About once a month</t>
+          <t>Several times a month</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>several_times_a_month</t>
+          <t>every_2_weeks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Several times a month</t>
+          <t>Every 2 weeks</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>every_2_weeks</t>
+          <t>every_week</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Every 2 weeks</t>
+          <t>Every week</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>every_week</t>
+          <t>more_than_once_a_week</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Every week</t>
+          <t>More than once a week</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>more_than_once_a_week</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>More than once a week</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1053,29 +1053,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>several_times_a_week</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Several times a week</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>healthcare_professional_citizenship_survey_form_section_2_choices</t>
+          <t>healthcare_professional_citizenship_survey_form_section_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>participate_in_quality_improvement_projects</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Participate in quality improvement projects</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>participate_in_quality_improvement_projects</t>
+          <t>lead_quality_improvement_projects</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Participate in quality improvement projects</t>
+          <t>Lead quality improvement projects</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>lead_quality_improvement_projects</t>
+          <t>develop_quality_improvement_tools</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lead quality improvement projects</t>
+          <t>Develop quality improvement tools</t>
         </is>
       </c>
     </row>
@@ -1121,29 +1121,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>develop_quality_improvement_tools</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Develop quality improvement tools</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>healthcare_professional_citizenship_survey_form_section_3_choices</t>
+          <t>healthcare_professional_citizenship_survey_form_section_4_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_likely</t>
+          <t>slightly_likely</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Not Likely</t>
+          <t>Slightly Likely</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>slightly_likely</t>
+          <t>moderately_likely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Slightly Likely</t>
+          <t>Moderately Likely</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>moderately_likely</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Moderately Likely</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1206,29 +1206,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>very_likely</t>
+          <t>extremely_likely</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Very Likely</t>
+          <t>Extremely Likely</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>healthcare_professional_citizenship_survey_form_section_4_choices</t>
+          <t>healthcare_professional_citizenship_survey_form_section_4_1_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>extremely_likely</t>
+          <t>participate_in_quality_improvement_projects</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Extremely Likely</t>
+          <t>Participate in quality improvement projects</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>participate_in_quality_improvement_projects</t>
+          <t>lead_quality_improvement_projects</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Participate in quality improvement projects</t>
+          <t>Lead quality improvement projects</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>lead_quality_improvement_projects</t>
+          <t>develop_quality_improvement_tools</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lead quality improvement projects</t>
+          <t>Develop quality improvement tools</t>
         </is>
       </c>
     </row>
@@ -1274,27 +1274,10 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>develop_quality_improvement_tools</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
-        <is>
-          <t>Develop quality improvement tools</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>healthcare_professional_citizenship_survey_form_section_4_1_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>other_(please_specify)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>Other (please specify)</t>
         </is>
